--- a/conference_registration_forms/024_digital_pedagogy_innovation_award_registration_form--conference_registration_forms.xlsx
+++ b/conference_registration_forms/024_digital_pedagogy_innovation_award_registration_form--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>submitter_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Main Page</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>submission</t>
+          <t>submitter_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>main_category</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Which category does your innovative pedagogical practice belong to?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>submission_0</t>
+          <t>award_title</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Award Title</t>
+          <t>Please describe your innovative pedagogical practice.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>What inspired you to submit this innovative pedagogical practice?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>submitter</t>
+          <t>submission_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name of the submitter</t>
+          <t>How did you implement your innovative pedagogical practice in your teaching?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>submitter_organisation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email of the submitter</t>
+          <t>Which submitter organisation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submitter_organisation</t>
+          <t>submission_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name of the submitter organisation</t>
+          <t>What is the name of your submission?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submission_2</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Which subcategory does your innovative pedagogical practice belong to?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>submission_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Main Category</t>
+          <t>Can you provide more details about your innovative pedagogical practice?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sub_categories</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>How will your innovative pedagogical practice benefit the students?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submission_3</t>
+          <t>submission_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Is this a team or individual submission?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submission_4</t>
+          <t>submission_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>What are some challenges you faced when implementing your innovative pedagogical practice?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submission_5</t>
+          <t>submission_7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>How do you intend to measure the impact of your innovative pedagogical practice?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission_6</t>
+          <t>submission_8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Are you willing to share any supporting materials or resources (e.g. images, videos, links) about your innovative pedagogical practice?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,64 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submission_7</t>
+          <t>submission_9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>What do you think will be the potential benefits and limitations of your innovative pedagogical practice for the students?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submission_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>submission_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -937,10 +891,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -965,7 +919,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>categories_choices</t>
+          <t>main_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -982,7 +936,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>categories_choices</t>
+          <t>main_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -991,6 +945,40 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>submission_5_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>submission_5_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
